--- a/ig/test-tabs-svs/CodeSystem-tre-r400-finess-statut-juridique.xlsx
+++ b/ig/test-tabs-svs/CodeSystem-tre-r400-finess-statut-juridique.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260223120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T12:00:00.000+00:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
